--- a/docs/templates/ir_excel_template_no_network.xlsx
+++ b/docs/templates/ir_excel_template_no_network.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,11 @@
           <t>jump_labels_used</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>flow_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -640,7 +645,6 @@
           <t>I0.0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -668,7 +672,6 @@
           <t>M10.0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,8 +694,6 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -715,8 +716,6 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -739,8 +738,6 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -763,8 +760,6 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
